--- a/test/fixtures/circular.xlsx
+++ b/test/fixtures/circular.xlsx
@@ -403,9 +403,11 @@
     <row r="1">
       <c r="A1">
         <f>B1+1</f>
+        <v>0</v>
       </c>
       <c r="B1">
         <f>A1+1</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
